--- a/data/export/2026-09-26-operations.xlsx
+++ b/data/export/2026-09-26-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:16</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:33</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,7 +2394,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2407,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2416,7 +2460,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2510,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2523,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2533,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2571,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2590,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2626,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2639,7 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2605,7 +2649,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2643,12 +2687,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2706,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2742,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2803,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2822,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2858,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2919,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2938,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2974,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3035,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3054,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,35 +3090,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3107,12 +3151,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3126,7 +3170,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3162,7 +3206,2831 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>70分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>4/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-operations.xlsx
+++ b/data/export/2026-09-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD47"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1025,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1868,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1892,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1912,7 +1964,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1922,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2079,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2042,7 +2094,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2199,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2157,12 +2209,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,41 +2440,45 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2455,12 +2511,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2474,7 +2530,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2499,46 +2555,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2571,12 +2631,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2590,7 +2650,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2615,46 +2675,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2687,12 +2751,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2706,7 +2770,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2731,46 +2795,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2803,12 +2871,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2822,7 +2890,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2847,46 +2915,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2919,12 +2991,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2938,7 +3010,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2963,46 +3035,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3035,12 +3111,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3054,7 +3130,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3079,46 +3155,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3151,12 +3231,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3170,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3195,46 +3275,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3267,12 +3351,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3286,7 +3370,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3311,18 +3395,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3423,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3345,7 +3433,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3355,40 +3443,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3402,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3412,33 +3504,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3451,22 +3547,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3499,12 +3595,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3518,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3543,7 +3639,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3554,7 +3650,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3567,60 +3663,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3634,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3644,17 +3744,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3664,13 +3764,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3787,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3693,7 +3797,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3703,40 +3807,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3750,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3760,33 +3868,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3911,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3809,7 +3921,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3847,12 +3959,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3866,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3902,7 +4014,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3915,22 +4027,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3963,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3982,7 +4094,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4018,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4143,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4041,7 +4153,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4079,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4098,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4134,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4147,22 +4259,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4195,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4214,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4250,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4263,22 +4375,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4311,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4330,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4366,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4379,22 +4491,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4427,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4446,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4482,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4607,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4543,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4562,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4598,7 +4710,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4611,22 +4723,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4659,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4678,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4714,77 +4826,73 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4808,107 +4916,99 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4922,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4932,107 +5032,99 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5046,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5056,17 +5148,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5076,87 +5168,79 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>70.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5170,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5180,17 +5264,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5200,45 +5284,41 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5271,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5290,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5326,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5387,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5406,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5442,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5508,7 +5588,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5522,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5558,35 +5638,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5619,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5638,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5663,50 +5743,46 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5739,7 +5815,7 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5794,25 +5870,25 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5822,7 +5898,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5855,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5910,35 +5986,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5971,12 +6047,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5990,47 +6066,3135 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X47" s="2" t="inlineStr">
+      <c r="X48" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
+      <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AD47" s="2" t="inlineStr">
-        <is>
-          <t>4/9</t>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>74分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-operations.xlsx
+++ b/data/export/2026-09-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2007,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2084,12 +2088,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2280,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2319,7 +2323,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2396,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2520,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2636,7 +2640,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2996,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3116,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3236,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3280,12 +3284,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3303,22 +3307,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,12 +3355,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3370,7 +3374,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3395,92 +3399,84 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3494,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3504,22 +3500,22 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3529,12 +3525,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3547,52 +3543,56 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3644,13 +3644,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3663,56 +3667,52 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:18</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3744,37 +3744,33 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3787,24 +3783,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3817,24 +3813,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3844,7 +3840,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3893,12 +3889,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3911,52 +3907,56 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3988,33 +3988,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4031,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4037,7 +4041,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4047,40 +4051,44 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4094,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4104,17 +4112,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4124,13 +4132,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4143,22 +4155,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4191,12 +4203,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4259,7 +4271,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4269,7 +4281,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4279,40 +4291,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4342,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,17 +4352,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4356,13 +4372,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4395,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4423,12 +4443,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4491,7 +4511,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4501,7 +4521,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4539,12 +4559,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4558,7 +4578,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4607,22 +4627,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4660,7 +4680,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4723,7 +4743,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4733,7 +4753,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4771,12 +4791,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4790,7 +4810,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4839,32 +4859,32 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq40，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4887,12 +4907,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4900,13 +4920,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 24分钟参与校验</t>
+        </is>
+      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4955,22 +4991,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5008,7 +5044,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5071,7 +5107,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5081,7 +5117,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5119,12 +5155,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5174,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5187,22 +5223,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5235,12 +5271,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5290,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5303,22 +5339,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5356,7 +5392,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5419,7 +5455,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5429,7 +5465,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5467,12 +5503,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5522,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5535,22 +5571,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5583,12 +5619,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5602,7 +5638,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5651,22 +5687,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5699,12 +5735,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5754,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5767,22 +5803,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5815,12 +5851,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5883,7 +5919,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5893,7 +5929,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5931,12 +5967,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5950,7 +5986,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5999,22 +6035,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6047,12 +6083,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6102,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6115,22 +6151,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6168,7 +6204,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6218,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,22 +6267,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6279,12 +6315,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6334,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6347,7 +6383,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6393,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6395,12 +6431,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6450,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6463,22 +6499,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6516,7 +6552,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6530,7 +6566,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6579,22 +6615,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6632,7 +6668,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6646,7 +6682,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6671,22 +6707,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6731,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6752,7 +6784,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6766,7 +6798,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6796,13 +6828,17 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6815,22 +6851,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6863,12 +6899,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6882,7 +6918,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6907,7 +6943,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6931,22 +6967,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6979,12 +7015,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6998,7 +7034,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7023,92 +7059,84 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7122,7 +7150,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7132,17 +7160,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7157,82 +7185,78 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7246,7 +7270,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7256,17 +7280,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7281,12 +7305,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7323,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7309,7 +7333,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7329,12 +7353,12 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -7356,7 +7380,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7370,7 +7394,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7405,12 +7429,12 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7447,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7433,7 +7457,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7453,24 +7477,24 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7480,7 +7504,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7494,7 +7518,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7529,12 +7553,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7571,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7557,7 +7581,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7567,40 +7591,44 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7614,7 +7642,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7624,17 +7652,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7644,13 +7672,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7695,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7673,7 +7705,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7693,29 +7725,29 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,7 +7766,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7769,12 +7801,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7819,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7797,7 +7829,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7817,34 +7849,34 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7858,7 +7890,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7883,22 +7915,22 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>7/12</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7943,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7921,7 +7953,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7931,32 +7963,36 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7964,7 +8000,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7978,7 +8014,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7988,17 +8024,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8013,12 +8049,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8067,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8041,7 +8077,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8051,40 +8087,44 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8098,7 +8138,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8108,17 +8148,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8128,13 +8168,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8191,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8157,7 +8201,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8195,12 +8239,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8214,7 +8258,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8239,18 +8283,22 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -8263,22 +8311,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8311,12 +8359,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8330,7 +8378,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8355,22 +8403,18 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -8383,22 +8427,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8431,12 +8475,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8450,7 +8494,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8475,22 +8519,18 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -8503,22 +8543,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8551,12 +8591,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8570,7 +8610,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8605,12 +8645,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -8623,22 +8663,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8671,12 +8711,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8690,7 +8730,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8715,18 +8755,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8783,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8749,7 +8793,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8787,7 +8831,7 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8806,7 +8850,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8831,18 +8875,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -8855,7 +8903,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8865,7 +8913,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8903,12 +8951,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8922,7 +8970,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8947,7 +8995,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8971,22 +9019,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -9019,12 +9067,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9038,7 +9086,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9087,22 +9135,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9135,12 +9183,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9154,45 +9202,281 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>7/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AC75" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AD73" s="2" t="inlineStr">
+      <c r="AD75" s="2" t="inlineStr">
         <is>
           <t>4/12</t>
         </is>

--- a/data/export/2026-09-26-operations.xlsx
+++ b/data/export/2026-09-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD75"/>
+  <dimension ref="A1:AD98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2017,24 +2017,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2188,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2284,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2308,17 +2316,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2328,13 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2367,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2400,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2424,37 +2440,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2487,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2520,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2544,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2607,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2640,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2664,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2727,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2760,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2784,17 +2812,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2804,17 +2832,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2847,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2880,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2904,37 +2936,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3039,7 +3071,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3054,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3159,7 +3191,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3174,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3289,12 +3321,12 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3392,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3404,13 +3436,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3520,87 +3556,83 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3646,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,65 +3656,65 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3715,12 +3747,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3734,7 +3766,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3759,88 +3791,88 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3854,7 +3886,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3864,107 +3896,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3978,7 +4006,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3988,107 +4016,103 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4102,7 +4126,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4112,65 +4136,65 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4203,12 +4227,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4222,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4247,18 +4271,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4271,24 +4299,24 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4301,24 +4329,24 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4328,7 +4356,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4342,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4367,22 +4395,22 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4423,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4405,7 +4433,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4443,12 +4471,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4462,7 +4490,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4487,7 +4515,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4498,7 +4526,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4539,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4521,7 +4549,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4531,40 +4559,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4578,7 +4610,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4588,33 +4620,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4627,60 +4663,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4694,7 +4734,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4704,33 +4744,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4743,60 +4787,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4810,7 +4858,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4820,33 +4868,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4859,60 +4911,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq40，推进2站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4920,29 +4976,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>物理seq24（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>08:02</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 24分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4952,33 +4992,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4991,60 +5035,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5058,7 +5106,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5068,33 +5116,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5159,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5117,7 +5169,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5127,40 +5179,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5174,7 +5230,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5184,33 +5240,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5223,22 +5283,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5271,12 +5331,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5290,7 +5350,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5315,7 +5375,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5326,7 +5386,7 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5399,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5349,7 +5409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5359,40 +5419,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5406,7 +5470,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5416,17 +5480,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5436,13 +5500,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5523,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5465,7 +5533,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5475,40 +5543,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5522,7 +5594,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5532,33 +5604,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5647,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5581,7 +5657,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5591,12 +5667,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5619,12 +5695,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5632,13 +5708,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 24分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5674,7 +5766,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5779,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5697,7 +5789,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5707,40 +5799,44 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5754,7 +5850,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5764,17 +5860,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5784,13 +5880,17 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5903,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5813,7 +5913,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5823,40 +5923,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5870,7 +5974,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5880,33 +5984,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5919,32 +6027,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq53，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5967,12 +6075,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5980,13 +6088,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6022,7 +6142,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6155,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6045,7 +6165,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6083,12 +6203,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6102,7 +6222,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6138,7 +6258,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6271,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6161,7 +6281,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6199,12 +6319,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6218,7 +6338,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6254,7 +6374,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6267,22 +6387,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6315,12 +6435,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6334,7 +6454,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6370,7 +6490,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6503,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6431,12 +6551,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6450,7 +6570,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6486,7 +6606,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6619,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6509,7 +6629,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6547,12 +6667,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6566,7 +6686,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6602,7 +6722,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6735,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6625,7 +6745,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6663,12 +6783,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6682,7 +6802,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6718,7 +6838,7 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6731,22 +6851,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6779,12 +6899,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6798,7 +6918,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6823,22 +6943,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6851,22 +6967,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6904,7 +7020,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6918,7 +7034,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6943,7 +7059,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6954,7 +7070,7 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6967,22 +7083,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7015,12 +7131,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7034,7 +7150,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7070,7 +7186,7 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7199,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7093,7 +7209,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7131,12 +7247,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7150,7 +7266,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7175,22 +7291,18 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7203,22 +7315,22 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7256,7 +7368,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7270,7 +7382,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7295,92 +7407,84 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7394,7 +7498,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7404,107 +7508,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7518,7 +7614,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7528,17 +7624,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7553,82 +7649,78 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7642,7 +7734,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7652,17 +7744,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7672,87 +7764,79 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7766,7 +7850,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7776,107 +7860,99 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7890,7 +7966,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7900,17 +7976,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7925,82 +8001,78 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8014,7 +8086,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8024,17 +8096,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8049,82 +8121,78 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8138,7 +8206,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8148,65 +8216,65 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8239,12 +8307,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8258,7 +8326,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8293,40 +8361,40 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8359,12 +8427,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8378,7 +8446,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8403,46 +8471,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8475,12 +8547,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8494,7 +8566,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8519,46 +8591,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8591,12 +8667,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8610,7 +8686,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8635,50 +8711,46 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8711,12 +8783,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8730,7 +8802,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8760,45 +8832,41 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8831,12 +8899,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8850,7 +8918,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8885,40 +8953,40 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8951,12 +9019,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8970,7 +9038,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8995,18 +9063,22 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9091,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9029,7 +9101,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9039,40 +9111,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9086,7 +9162,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9096,33 +9172,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9215,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9145,7 +9225,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9155,40 +9235,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9202,7 +9286,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9212,37 +9296,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>7/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9255,60 +9339,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9322,7 +9410,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9332,33 +9420,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9371,60 +9463,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9438,47 +9534,2819 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="X88" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AC89" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AD75" s="2" t="inlineStr">
-        <is>
-          <t>4/12</t>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-operations.xlsx
+++ b/data/export/2026-09-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD175"/>
+  <dimension ref="A1:AD178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3576,17 +3576,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5847,32 +5847,36 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5880,7 +5884,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5904,17 +5908,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5924,12 +5928,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
@@ -5967,32 +5971,36 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6000,7 +6008,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6024,17 +6032,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6044,17 +6052,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6240,7 +6248,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6360,7 +6368,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6480,7 +6488,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6600,7 +6608,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6720,7 +6728,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6774,7 +6782,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6848,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6884,17 +6892,17 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6972,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7018,7 +7026,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7092,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7262,7 +7270,7 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7340,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7386,7 +7394,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7464,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7505,12 +7513,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7712,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7758,7 +7766,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7836,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7877,12 +7885,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7956,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8002,7 +8010,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8134,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8258,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8324,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8371,18 +8379,22 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8464,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8696,7 +8708,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8878,7 +8890,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8960,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9002,7 +9014,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9208,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9374,7 +9386,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9572,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9614,7 +9626,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9750,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9820,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9862,7 +9874,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9994,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10118,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10188,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10230,7 +10242,7 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10312,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10354,7 +10366,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10436,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10726,7 +10738,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10808,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10850,7 +10862,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10920,7 +10932,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10969,12 +10981,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11056,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11098,7 +11110,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11304,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11341,12 +11353,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11424,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11548,7 +11560,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11602,7 +11614,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11734,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11858,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12048,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12160,7 +12172,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12214,7 +12226,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12350,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12544,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12710,7 +12722,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12792,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12834,7 +12846,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12970,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13040,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13082,7 +13094,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13164,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13206,7 +13218,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13276,7 +13288,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13330,7 +13342,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13373,24 +13385,24 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
@@ -13400,7 +13412,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13449,12 +13461,12 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13509,12 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
@@ -13524,7 +13536,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13573,12 +13585,12 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13628,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq46，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -13644,7 +13656,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13776,7 +13788,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13830,7 +13842,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13863,32 +13875,36 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N109" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -13896,7 +13912,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13920,33 +13936,37 @@
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC109" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14032,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14132,7 +14152,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14248,7 +14268,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14368,7 +14388,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14422,7 +14442,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14508,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14542,7 +14562,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14628,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14662,7 +14682,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14748,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14782,7 +14802,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -14848,7 +14868,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14902,7 +14922,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14988,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15022,7 +15042,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15108,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15208,7 +15228,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15257,12 +15277,12 @@
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -15328,7 +15348,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15382,77 +15402,73 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N122" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15466,7 +15482,7 @@
       <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="W122" s="2" t="inlineStr">
@@ -15476,37 +15492,37 @@
       </c>
       <c r="X122" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y122" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z122" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA122" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -15519,24 +15535,24 @@
       <c r="B123" s="2" t="inlineStr"/>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -15549,19 +15565,19 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -15571,12 +15587,12 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15590,7 +15606,7 @@
       <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
@@ -15615,22 +15631,22 @@
       </c>
       <c r="AA123" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -15643,24 +15659,24 @@
       <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -15673,19 +15689,19 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -15695,12 +15711,12 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15714,7 +15730,7 @@
       <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W124" s="2" t="inlineStr">
@@ -15739,22 +15755,22 @@
       </c>
       <c r="AA124" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -15767,24 +15783,24 @@
       <c r="B125" s="2" t="inlineStr"/>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -15797,34 +15813,34 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15838,7 +15854,7 @@
       <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W125" s="2" t="inlineStr">
@@ -15868,17 +15884,17 @@
       </c>
       <c r="AB125" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -15891,24 +15907,24 @@
       <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -15921,34 +15937,34 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15962,7 +15978,7 @@
       <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W126" s="2" t="inlineStr">
@@ -15987,7 +16003,7 @@
       </c>
       <c r="AA126" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB126" s="2" t="inlineStr">
@@ -15997,12 +16013,12 @@
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -16015,24 +16031,24 @@
       <c r="B127" s="2" t="inlineStr"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16045,34 +16061,34 @@
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16086,7 +16102,7 @@
       <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W127" s="2" t="inlineStr">
@@ -16111,22 +16127,22 @@
       </c>
       <c r="AA127" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB127" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB127" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -16139,24 +16155,24 @@
       <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16169,34 +16185,34 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16210,7 +16226,7 @@
       <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
@@ -16235,7 +16251,7 @@
       </c>
       <c r="AA128" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB128" s="2" t="inlineStr">
@@ -16245,12 +16261,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -16263,24 +16279,24 @@
       <c r="B129" s="2" t="inlineStr"/>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>07:40</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16293,19 +16309,19 @@
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -16315,12 +16331,12 @@
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16334,7 +16350,7 @@
       <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W129" s="2" t="inlineStr">
@@ -16359,22 +16375,22 @@
       </c>
       <c r="AA129" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -16387,24 +16403,24 @@
       <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16417,12 +16433,12 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
@@ -16439,12 +16455,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16458,7 +16474,7 @@
       <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
@@ -16483,22 +16499,22 @@
       </c>
       <c r="AA130" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB130" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC130" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -16511,24 +16527,24 @@
       <c r="B131" s="2" t="inlineStr"/>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16541,19 +16557,19 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -16563,12 +16579,12 @@
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16582,7 +16598,7 @@
       <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W131" s="2" t="inlineStr">
@@ -16607,7 +16623,7 @@
       </c>
       <c r="AA131" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB131" s="2" t="inlineStr">
@@ -16617,12 +16633,12 @@
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16651,7 @@
       <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -16645,7 +16661,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -16665,7 +16681,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -16677,22 +16693,22 @@
       <c r="L132" s="2" t="inlineStr"/>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16706,7 +16722,7 @@
       <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
@@ -16736,17 +16752,17 @@
       </c>
       <c r="AB132" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -16759,24 +16775,24 @@
       <c r="B133" s="2" t="inlineStr"/>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -16789,34 +16805,34 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16855,22 +16871,22 @@
       </c>
       <c r="AA133" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16899,7 @@
       <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -16893,7 +16909,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -16903,32 +16919,36 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N134" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -16936,7 +16956,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -16950,7 +16970,7 @@
       <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
@@ -16960,37 +16980,37 @@
       </c>
       <c r="X134" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y134" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z134" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA134" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -17003,64 +17023,60 @@
       <c r="B135" s="2" t="inlineStr"/>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N135" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17084,37 +17100,37 @@
       </c>
       <c r="X135" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y135" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z135" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -17127,24 +17143,24 @@
       <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17157,12 +17173,12 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
@@ -17179,12 +17195,12 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17198,7 +17214,7 @@
       <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
@@ -17223,22 +17239,22 @@
       </c>
       <c r="AA136" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -17251,24 +17267,24 @@
       <c r="B137" s="2" t="inlineStr"/>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17281,34 +17297,34 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17357,12 +17373,12 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17391,7 @@
       <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -17385,7 +17401,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -17405,12 +17421,12 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
@@ -17427,12 +17443,12 @@
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17446,7 +17462,7 @@
       <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
@@ -17471,22 +17487,22 @@
       </c>
       <c r="AA138" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -17499,24 +17515,24 @@
       <c r="B139" s="2" t="inlineStr"/>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17529,29 +17545,29 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P139" s="2" t="inlineStr">
@@ -17595,22 +17611,22 @@
       </c>
       <c r="AA139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -17623,24 +17639,24 @@
       <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17653,34 +17669,34 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17694,7 +17710,7 @@
       <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W140" s="2" t="inlineStr">
@@ -17724,17 +17740,17 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -17747,24 +17763,24 @@
       <c r="B141" s="2" t="inlineStr"/>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17777,24 +17793,24 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
@@ -17804,7 +17820,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17818,7 +17834,7 @@
       <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W141" s="2" t="inlineStr">
@@ -17843,22 +17859,22 @@
       </c>
       <c r="AA141" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -17871,24 +17887,24 @@
       <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -17901,34 +17917,34 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -17942,7 +17958,7 @@
       <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W142" s="2" t="inlineStr">
@@ -17967,7 +17983,7 @@
       </c>
       <c r="AA142" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB142" s="2" t="inlineStr">
@@ -17977,12 +17993,12 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -17995,24 +18011,24 @@
       <c r="B143" s="2" t="inlineStr"/>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18025,12 +18041,12 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
@@ -18047,12 +18063,12 @@
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18066,7 +18082,7 @@
       <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
@@ -18091,22 +18107,22 @@
       </c>
       <c r="AA143" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -18119,24 +18135,24 @@
       <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18149,12 +18165,12 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
@@ -18171,12 +18187,12 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18190,7 +18206,7 @@
       <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
@@ -18215,22 +18231,22 @@
       </c>
       <c r="AA144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -18243,60 +18259,64 @@
       <c r="B145" s="2" t="inlineStr"/>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr"/>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N145" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18310,7 +18330,7 @@
       <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W145" s="2" t="inlineStr">
@@ -18320,22 +18340,22 @@
       </c>
       <c r="X145" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y145" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z145" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA145" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB145" s="2" t="inlineStr">
@@ -18345,12 +18365,12 @@
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -18363,64 +18383,60 @@
       <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N146" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18434,7 +18450,7 @@
       <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
@@ -18444,37 +18460,37 @@
       </c>
       <c r="X146" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y146" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z146" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA146" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB146" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC146" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -18487,24 +18503,24 @@
       <c r="B147" s="2" t="inlineStr"/>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18517,34 +18533,34 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18558,7 +18574,7 @@
       <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W147" s="2" t="inlineStr">
@@ -18583,22 +18599,22 @@
       </c>
       <c r="AA147" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB147" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -18611,24 +18627,24 @@
       <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18641,12 +18657,12 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
@@ -18663,12 +18679,12 @@
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18682,7 +18698,7 @@
       <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W148" s="2" t="inlineStr">
@@ -18712,17 +18728,17 @@
       </c>
       <c r="AB148" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC148" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -18735,24 +18751,24 @@
       <c r="B149" s="2" t="inlineStr"/>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -18765,12 +18781,12 @@
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
@@ -18787,12 +18803,12 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18806,7 +18822,7 @@
       <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
@@ -18831,22 +18847,22 @@
       </c>
       <c r="AA149" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB149" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC149" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -18859,60 +18875,64 @@
       <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N150" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -18926,7 +18946,7 @@
       <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W150" s="2" t="inlineStr">
@@ -18936,37 +18956,37 @@
       </c>
       <c r="X150" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y150" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z150" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA150" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -18979,64 +18999,60 @@
       <c r="B151" s="2" t="inlineStr"/>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr"/>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N151" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr"/>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19050,7 +19066,7 @@
       <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="W151" s="2" t="inlineStr">
@@ -19060,37 +19076,37 @@
       </c>
       <c r="X151" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y151" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z151" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA151" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB151" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB151" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -19103,24 +19119,24 @@
       <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -19133,29 +19149,29 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P152" s="2" t="inlineStr">
@@ -19199,22 +19215,22 @@
       </c>
       <c r="AA152" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -19227,7 +19243,7 @@
       <c r="B153" s="2" t="inlineStr"/>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -19237,7 +19253,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -19257,34 +19273,34 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19298,7 +19314,7 @@
       <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W153" s="2" t="inlineStr">
@@ -19323,7 +19339,7 @@
       </c>
       <c r="AA153" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB153" s="2" t="inlineStr">
@@ -19333,12 +19349,12 @@
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -19351,52 +19367,56 @@
       <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N154" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -19404,7 +19424,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19418,7 +19438,7 @@
       <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="W154" s="2" t="inlineStr">
@@ -19428,37 +19448,37 @@
       </c>
       <c r="X154" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA154" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB154" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB154" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -19471,64 +19491,60 @@
       <c r="B155" s="2" t="inlineStr"/>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr"/>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N155" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr"/>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19542,7 +19558,7 @@
       <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W155" s="2" t="inlineStr">
@@ -19552,37 +19568,37 @@
       </c>
       <c r="X155" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y155" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z155" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA155" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -19595,7 +19611,7 @@
       <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -19605,7 +19621,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -19625,12 +19641,12 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
@@ -19647,12 +19663,12 @@
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19666,7 +19682,7 @@
       <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="W156" s="2" t="inlineStr">
@@ -19696,17 +19712,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -19719,60 +19735,64 @@
       <c r="B157" s="2" t="inlineStr"/>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr"/>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N157" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19796,32 +19816,32 @@
       </c>
       <c r="X157" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y157" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z157" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA157" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -19839,64 +19859,60 @@
       <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N158" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr"/>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19910,7 +19926,7 @@
       <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
@@ -19920,37 +19936,37 @@
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y158" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z158" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA158" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -19963,24 +19979,24 @@
       <c r="B159" s="2" t="inlineStr"/>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -19993,12 +20009,12 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr"/>
@@ -20015,12 +20031,12 @@
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20034,7 +20050,7 @@
       <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="W159" s="2" t="inlineStr">
@@ -20059,22 +20075,22 @@
       </c>
       <c r="AA159" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -20087,24 +20103,24 @@
       <c r="B160" s="2" t="inlineStr"/>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -20117,12 +20133,12 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
@@ -20139,12 +20155,12 @@
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20158,7 +20174,7 @@
       <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="W160" s="2" t="inlineStr">
@@ -20183,17 +20199,17 @@
       </c>
       <c r="AA160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
@@ -20211,24 +20227,24 @@
       <c r="B161" s="2" t="inlineStr"/>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -20241,34 +20257,34 @@
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr"/>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20282,7 +20298,7 @@
       <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="W161" s="2" t="inlineStr">
@@ -20307,22 +20323,22 @@
       </c>
       <c r="AA161" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -20335,24 +20351,24 @@
       <c r="B162" s="2" t="inlineStr"/>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -20365,34 +20381,34 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr"/>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20406,7 +20422,7 @@
       <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="W162" s="2" t="inlineStr">
@@ -20431,7 +20447,7 @@
       </c>
       <c r="AA162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB162" s="2" t="inlineStr">
@@ -20459,24 +20475,24 @@
       <c r="B163" s="2" t="inlineStr"/>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -20489,24 +20505,24 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr"/>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -20516,7 +20532,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20530,7 +20546,7 @@
       <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="W163" s="2" t="inlineStr">
@@ -20555,22 +20571,22 @@
       </c>
       <c r="AA163" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -20583,24 +20599,24 @@
       <c r="B164" s="2" t="inlineStr"/>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -20613,34 +20629,34 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr"/>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20654,7 +20670,7 @@
       <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="W164" s="2" t="inlineStr">
@@ -20679,7 +20695,7 @@
       </c>
       <c r="AA164" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB164" s="2" t="inlineStr">
@@ -20689,12 +20705,12 @@
       </c>
       <c r="AC164" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -20707,60 +20723,64 @@
       <c r="B165" s="2" t="inlineStr"/>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr"/>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N165" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20774,7 +20794,7 @@
       <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="W165" s="2" t="inlineStr">
@@ -20784,33 +20804,37 @@
       </c>
       <c r="X165" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y165" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z165" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA165" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC165" s="2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC165" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -20823,64 +20847,60 @@
       <c r="B166" s="2" t="inlineStr"/>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr"/>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N166" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr"/>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20894,7 +20914,7 @@
       <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="W166" s="2" t="inlineStr">
@@ -20904,37 +20924,33 @@
       </c>
       <c r="X166" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y166" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z166" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA166" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC166" s="2" t="inlineStr">
-        <is>
-          <t>83.8</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC166" s="2" t="inlineStr"/>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -20947,60 +20963,64 @@
       <c r="B167" s="2" t="inlineStr"/>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr"/>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N167" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21014,7 +21034,7 @@
       <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="W167" s="2" t="inlineStr">
@@ -21024,37 +21044,37 @@
       </c>
       <c r="X167" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y167" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z167" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA167" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -21067,60 +21087,64 @@
       <c r="B168" s="2" t="inlineStr"/>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N168" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21134,7 +21158,7 @@
       <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="W168" s="2" t="inlineStr">
@@ -21144,17 +21168,17 @@
       </c>
       <c r="X168" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y168" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z168" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA168" s="2" t="inlineStr">
@@ -21164,17 +21188,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -21187,22 +21211,22 @@
       <c r="B169" s="2" t="inlineStr"/>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
@@ -21235,12 +21259,12 @@
       <c r="N169" s="2" t="inlineStr"/>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21254,7 +21278,7 @@
       <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="W169" s="2" t="inlineStr">
@@ -21289,12 +21313,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -21307,22 +21331,22 @@
       <c r="B170" s="2" t="inlineStr"/>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -21355,12 +21379,12 @@
       <c r="N170" s="2" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21374,7 +21398,7 @@
       <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="W170" s="2" t="inlineStr">
@@ -21399,22 +21423,22 @@
       </c>
       <c r="AA170" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -21427,22 +21451,22 @@
       <c r="B171" s="2" t="inlineStr"/>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
@@ -21475,12 +21499,12 @@
       <c r="N171" s="2" t="inlineStr"/>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21494,7 +21518,7 @@
       <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="W171" s="2" t="inlineStr">
@@ -21519,22 +21543,22 @@
       </c>
       <c r="AA171" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB171" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB171" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -21547,7 +21571,7 @@
       <c r="B172" s="2" t="inlineStr"/>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -21557,7 +21581,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -21595,12 +21619,12 @@
       <c r="N172" s="2" t="inlineStr"/>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21614,7 +21638,7 @@
       <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="W172" s="2" t="inlineStr">
@@ -21639,7 +21663,7 @@
       </c>
       <c r="AA172" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB172" s="2" t="inlineStr">
@@ -21649,12 +21673,12 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -21667,22 +21691,22 @@
       <c r="B173" s="2" t="inlineStr"/>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
@@ -21715,12 +21739,12 @@
       <c r="N173" s="2" t="inlineStr"/>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21759,18 +21783,22 @@
       </c>
       <c r="AA173" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB173" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB173" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC173" s="2" t="inlineStr"/>
+      <c r="AC173" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -21783,22 +21811,22 @@
       <c r="B174" s="2" t="inlineStr"/>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E174" s="2" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
@@ -21831,12 +21859,12 @@
       <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21850,7 +21878,7 @@
       <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="W174" s="2" t="inlineStr">
@@ -21875,22 +21903,18 @@
       </c>
       <c r="AA174" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC174" s="2" t="inlineStr">
-        <is>
-          <t>84.3</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC174" s="2" t="inlineStr"/>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -21903,22 +21927,22 @@
       <c r="B175" s="2" t="inlineStr"/>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
@@ -21951,12 +21975,12 @@
       <c r="N175" s="2" t="inlineStr"/>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -21970,47 +21994,407 @@
       <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" s="2" t="inlineStr">
         <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA175" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB175" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC175" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AD175" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
           <t>14:55</t>
         </is>
       </c>
-      <c r="W175" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr"/>
+      <c r="S176" s="2" t="inlineStr"/>
+      <c r="T176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X175" s="2" t="inlineStr">
+      <c r="X176" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y175" s="2" t="inlineStr">
+      <c r="Y176" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Z175" s="2" t="inlineStr">
+      <c r="Z176" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA175" s="2" t="inlineStr">
+      <c r="AA176" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB175" s="2" t="inlineStr">
+      <c r="AB176" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC176" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AD176" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr"/>
+      <c r="S177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X177" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y177" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA177" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC177" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AD177" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr"/>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB178" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC175" s="2" t="inlineStr">
-        <is>
-          <t>79.5</t>
-        </is>
-      </c>
-      <c r="AD175" s="2" t="inlineStr">
-        <is>
-          <t>3/15</t>
+      <c r="AC178" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD178" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-26-operations.xlsx
+++ b/data/export/2026-09-26-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5432,17 +5432,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6796,17 +6796,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7292,17 +7292,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8284,17 +8284,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9276,17 +9276,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9524,17 +9524,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9713,12 +9713,12 @@
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9837,12 +9837,12 @@
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9939,32 +9939,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9972,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9996,17 +10000,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10016,12 +10020,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10059,32 +10063,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10092,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10116,17 +10124,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10136,17 +10144,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -10179,32 +10187,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10212,7 +10224,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10236,17 +10248,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10256,17 +10268,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10452,7 +10464,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10496,12 +10508,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
@@ -10630,7 +10642,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10762,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10832,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -11122,7 +11134,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11204,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11316,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11360,17 +11372,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11506,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11626,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11696,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11808,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11852,17 +11864,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11998,7 +12010,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12134,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12204,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12236,17 +12248,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12444,7 +12456,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12498,7 +12510,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12634,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12704,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12746,7 +12758,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12882,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12994,7 +13006,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13316,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13353,7 +13365,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
@@ -13482,7 +13494,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13560,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13672,7 +13684,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13716,12 +13728,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
@@ -13974,7 +13986,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14110,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14304,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14594,7 +14606,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14676,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14708,17 +14720,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14800,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14966,7 +14978,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15234,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15300,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15332,17 +15344,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -15412,7 +15424,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15532,7 +15544,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15576,17 +15588,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -15710,7 +15722,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15846,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15916,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15958,7 +15970,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16040,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16082,7 +16094,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16206,7 +16218,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -16330,7 +16342,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16536,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16826,7 +16838,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17074,7 +17086,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -17198,7 +17210,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -17454,7 +17466,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17578,7 +17590,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -17702,7 +17714,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17784,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17950,7 +17962,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18086,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -18322,7 +18334,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -18566,7 +18578,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18814,7 +18826,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18946,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19016,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19048,17 +19060,17 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -19310,7 +19322,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -19376,7 +19388,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19420,17 +19432,17 @@
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19500,7 +19512,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19549,7 +19561,7 @@
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
@@ -19624,7 +19636,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19668,12 +19680,12 @@
       </c>
       <c r="AB155" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
@@ -19748,7 +19760,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19792,17 +19804,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19872,7 +19884,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19996,7 +20008,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20050,7 +20062,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -20116,7 +20128,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20240,7 +20252,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20360,7 +20372,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20480,7 +20492,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20654,7 +20666,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20786,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20910,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -21022,7 +21034,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -21092,7 +21104,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21146,7 +21158,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21270,7 +21282,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21394,7 +21406,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21526,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -21803,32 +21815,36 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -21836,7 +21852,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21860,17 +21876,17 @@
       </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z173" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA173" s="2" t="inlineStr">
@@ -21880,17 +21896,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21933,24 +21949,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21960,7 +21976,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22009,7 +22025,7 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
@@ -22047,32 +22063,36 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -22080,7 +22100,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22104,17 +22124,17 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA175" s="2" t="inlineStr">
@@ -22124,13 +22144,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC175" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC175" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -22163,12 +22187,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -22196,7 +22220,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22204,10 +22228,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R176" s="2" t="inlineStr"/>
-      <c r="S176" s="2" t="inlineStr"/>
-      <c r="T176" s="2" t="inlineStr"/>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V176" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22283,32 +22323,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22316,7 +22360,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22340,17 +22384,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22360,12 +22404,12 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
@@ -22403,32 +22447,36 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -22436,7 +22484,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22460,17 +22508,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22480,17 +22528,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22604,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22676,7 +22724,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22763,32 +22811,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -22796,7 +22848,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22820,17 +22872,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22840,17 +22892,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22916,7 +22968,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22970,7 +23022,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -23036,7 +23088,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23156,7 +23208,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23276,7 +23328,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23330,7 +23382,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -23400,7 +23452,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23772,7 +23824,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -24020,7 +24072,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24069,7 +24121,7 @@
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
@@ -24268,7 +24320,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24392,7 +24444,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24516,7 +24568,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24560,12 +24612,12 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
@@ -24884,7 +24936,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -25008,7 +25060,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25052,12 +25104,12 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
@@ -25504,7 +25556,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25553,7 +25605,7 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -25628,7 +25680,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25672,12 +25724,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25752,7 +25804,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25796,7 +25848,7 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
@@ -26000,7 +26052,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26124,7 +26176,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26244,7 +26296,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26288,12 +26340,12 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26616,7 +26668,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26740,7 +26792,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26784,12 +26836,12 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
@@ -27108,7 +27160,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27157,7 +27209,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27232,7 +27284,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27276,7 +27328,7 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
@@ -27352,7 +27404,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27396,12 +27448,12 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27476,7 +27528,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27600,7 +27652,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27644,12 +27696,12 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -28092,7 +28144,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28136,12 +28188,12 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28340,7 +28392,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28384,12 +28436,12 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28464,7 +28516,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28508,7 +28560,7 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
@@ -28708,7 +28760,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28752,17 +28804,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29204,7 +29256,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29328,7 +29380,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29372,7 +29424,7 @@
       </c>
       <c r="AB234" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC234" s="2" t="inlineStr">
@@ -29452,7 +29504,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29576,7 +29628,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29620,12 +29672,12 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
@@ -29700,7 +29752,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29744,17 +29796,17 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30196,7 +30248,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30240,12 +30292,12 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
@@ -30320,7 +30372,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30568,7 +30620,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30692,7 +30744,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30741,7 +30793,7 @@
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
@@ -30816,7 +30868,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q246" s="2" t="inlineStr">
@@ -30860,12 +30912,12 @@
       </c>
       <c r="AB246" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC246" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD246" s="2" t="inlineStr">
@@ -30936,7 +30988,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -30980,7 +31032,7 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
@@ -31056,7 +31108,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31100,12 +31152,12 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
@@ -31300,7 +31352,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31344,17 +31396,17 @@
       </c>
       <c r="AB250" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -31668,7 +31720,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31712,12 +31764,12 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
@@ -31792,7 +31844,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -32164,7 +32216,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32213,7 +32265,7 @@
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
@@ -32288,7 +32340,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32412,7 +32464,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32456,7 +32508,7 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
@@ -32536,7 +32588,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32580,12 +32632,12 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
@@ -32660,7 +32712,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32784,7 +32836,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32828,17 +32880,17 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -33268,7 +33320,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33312,12 +33364,12 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33388,7 +33440,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33512,7 +33564,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33556,12 +33608,12 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33884,7 +33936,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33981,24 +34033,24 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr"/>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N272" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O272" s="2" t="inlineStr">
@@ -34008,7 +34060,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34057,7 +34109,7 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
@@ -34095,32 +34147,36 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr"/>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N273" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O273" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34128,7 +34184,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34152,17 +34208,17 @@
       </c>
       <c r="X273" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y273" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z273" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA273" s="2" t="inlineStr">
@@ -34172,7 +34228,7 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
@@ -34372,7 +34428,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34459,32 +34515,36 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr"/>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N276" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O276" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34492,7 +34552,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34516,17 +34576,17 @@
       </c>
       <c r="X276" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y276" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z276" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA276" s="2" t="inlineStr">
@@ -34536,12 +34596,12 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
@@ -34612,7 +34672,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34699,32 +34759,36 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N278" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O278" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -34732,7 +34796,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34756,17 +34820,17 @@
       </c>
       <c r="X278" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA278" s="2" t="inlineStr">
@@ -34776,17 +34840,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34819,32 +34883,36 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O279" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -34852,7 +34920,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34876,17 +34944,17 @@
       </c>
       <c r="X279" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA279" s="2" t="inlineStr">
@@ -34896,12 +34964,12 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
@@ -34939,32 +35007,36 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N280" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O280" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -34972,7 +35044,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -34996,17 +35068,17 @@
       </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA280" s="2" t="inlineStr">
@@ -35016,12 +35088,12 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
@@ -35092,7 +35164,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35136,12 +35208,12 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35212,7 +35284,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35256,17 +35328,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
